--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 20:15</t>
+          <t>更新时间: 2026-08-09 20:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 20:55</t>
+          <t>更新时间: 2026-08-10 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-10 17:01</t>
+          <t>更新时间: 2026-08-11 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 12:21</t>
+          <t>更新时间: 2026-08-11 12:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 13:31</t>
+          <t>更新时间: 2026-08-12 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 13:32</t>
+          <t>更新时间: 2026-08-14 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 16:42</t>
+          <t>更新时间: 2026-08-15 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 08:14</t>
+          <t>更新时间: 2026-08-15 11:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 12:06</t>
+          <t>更新时间: 2026-08-15 13:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 13:01</t>
+          <t>更新时间: 2026-08-16 08:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 08:12</t>
+          <t>更新时间: 2026-08-16 11:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 11:29</t>
+          <t>更新时间: 2026-08-16 11:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 13:05</t>
+          <t>更新时间: 2026-08-17 08:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 08:09</t>
+          <t>更新时间: 2026-08-17 11:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 11:36</t>
+          <t>更新时间: 2026-08-17 12:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 12:26</t>
+          <t>更新时间: 2026-08-17 13:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 13:53</t>
+          <t>更新时间: 2026-08-18 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:13</t>
+          <t>更新时间: 2026-08-18 11:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 11:13</t>
+          <t>更新时间: 2026-08-18 11:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 11:28</t>
+          <t>更新时间: 2026-08-18 12:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 08:12</t>
+          <t>更新时间: 2026-08-19 11:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 11:25</t>
+          <t>更新时间: 2026-08-19 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 13:16</t>
+          <t>更新时间: 2026-08-20 08:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 08:15</t>
+          <t>更新时间: 2026-08-20 11:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 12:21</t>
+          <t>更新时间: 2026-08-20 13:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 13:18</t>
+          <t>更新时间: 2026-08-21 08:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 08:16</t>
+          <t>更新时间: 2026-08-21 11:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 11:33</t>
+          <t>更新时间: 2026-08-21 11:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 11:38</t>
+          <t>更新时间: 2026-08-21 12:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 12:23</t>
+          <t>更新时间: 2026-08-21 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 13:16</t>
+          <t>更新时间: 2026-08-24 08:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 08:11</t>
+          <t>更新时间: 2026-08-24 11:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:58</t>
+          <t>更新时间: 2026-08-25 08:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 08:16</t>
+          <t>更新时间: 2026-08-25 11:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 08:14</t>
+          <t>更新时间: 2026-08-26 11:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 14:57</t>
+          <t>更新时间: 2026-08-28 15:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 15:06</t>
+          <t>更新时间: 2026-08-29 05:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 05:26</t>
+          <t>更新时间: 2026-08-29 07:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 07:37</t>
+          <t>更新时间: 2026-08-29 08:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 08:20</t>
+          <t>更新时间: 2026-08-29 09:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 09:05</t>
+          <t>更新时间: 2026-08-29 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 10:24</t>
+          <t>更新时间: 2026-08-29 12:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 12:03</t>
+          <t>更新时间: 2026-08-30 07:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 07:58</t>
+          <t>更新时间: 2026-08-30 08:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 08:21</t>
+          <t>更新时间: 2026-08-30 09:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 09:03</t>
+          <t>更新时间: 2026-08-30 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 10:24</t>
+          <t>更新时间: 2026-08-30 12:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 12:04</t>
+          <t>更新时间: 2026-08-31 07:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 07:52</t>
+          <t>更新时间: 2026-08-31 08:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 08:20</t>
+          <t>更新时间: 2026-08-31 09:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 09:03</t>
+          <t>更新时间: 2026-08-31 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 10:24</t>
+          <t>更新时间: 2026-08-31 12:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 12:04</t>
+          <t>更新时间: 2026-09-01 07:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 07:48</t>
+          <t>更新时间: 2026-09-01 08:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 08:37</t>
+          <t>更新时间: 2026-09-01 09:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 09:07</t>
+          <t>更新时间: 2026-09-01 10:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 10:29</t>
+          <t>更新时间: 2026-09-01 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 12:06</t>
+          <t>更新时间: 2026-09-02 09:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 09:27</t>
+          <t>更新时间: 2026-09-02 12:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 12:34</t>
+          <t>更新时间: 2026-09-02 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:22</t>
+          <t>更新时间: 2026-09-02 15:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 15:09</t>
+          <t>更新时间: 2026-09-02 16:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 16:19</t>
+          <t>更新时间: 2026-09-03 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 09:32</t>
+          <t>更新时间: 2026-09-03 12:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 12:33</t>
+          <t>更新时间: 2026-09-03 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:25</t>
+          <t>更新时间: 2026-09-03 15:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 15:13</t>
+          <t>更新时间: 2026-09-03 16:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 16:28</t>
+          <t>更新时间: 2026-09-04 09:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 09:27</t>
+          <t>更新时间: 2026-09-04 12:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 12:34</t>
+          <t>更新时间: 2026-09-04 13:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:23</t>
+          <t>更新时间: 2026-09-04 15:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 15:16</t>
+          <t>更新时间: 2026-09-04 16:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 16:24</t>
+          <t>更新时间: 2026-09-05 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 09:32</t>
+          <t>更新时间: 2026-09-05 12:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 12:29</t>
+          <t>更新时间: 2026-09-05 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:12</t>
+          <t>更新时间: 2026-09-05 14:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 14:58</t>
+          <t>更新时间: 2026-09-05 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 15:59</t>
+          <t>更新时间: 2026-09-06 09:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 09:30</t>
+          <t>更新时间: 2026-09-06 12:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 12:39</t>
+          <t>更新时间: 2026-09-06 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:26</t>
+          <t>更新时间: 2026-09-06 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 15:10</t>
+          <t>更新时间: 2026-09-06 16:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:17</t>
+          <t>更新时间: 2026-09-07 09:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:27</t>
+          <t>更新时间: 2026-09-07 12:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 12:41</t>
+          <t>更新时间: 2026-09-07 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:38</t>
+          <t>更新时间: 2026-09-07 15:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 15:22</t>
+          <t>更新时间: 2026-09-07 16:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 16:50</t>
+          <t>更新时间: 2026-09-08 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:32</t>
+          <t>更新时间: 2026-09-08 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 12:36</t>
+          <t>更新时间: 2026-09-08 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:33</t>
+          <t>更新时间: 2026-09-08 15:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 15:17</t>
+          <t>更新时间: 2026-09-08 16:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 16:30</t>
+          <t>更新时间: 2026-09-09 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:38</t>
+          <t>更新时间: 2026-09-09 12:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 12:42</t>
+          <t>更新时间: 2026-09-09 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:40</t>
+          <t>更新时间: 2026-09-09 15:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 15:26</t>
+          <t>更新时间: 2026-09-09 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 16:33</t>
+          <t>更新时间: 2026-09-10 09:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:34</t>
+          <t>更新时间: 2026-09-10 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 12:43</t>
+          <t>更新时间: 2026-09-10 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:31</t>
+          <t>更新时间: 2026-09-10 15:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 15:21</t>
+          <t>更新时间: 2026-09-10 16:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 16:34</t>
+          <t>更新时间: 2026-09-11 09:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:35</t>
+          <t>更新时间: 2026-09-11 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 12:40</t>
+          <t>更新时间: 2026-09-11 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:34</t>
+          <t>更新时间: 2026-09-11 15:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 15:20</t>
+          <t>更新时间: 2026-09-11 16:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 16:29</t>
+          <t>更新时间: 2026-09-12 09:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:40</t>
+          <t>更新时间: 2026-09-12 12:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 12:34</t>
+          <t>更新时间: 2026-09-12 13:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:19</t>
+          <t>更新时间: 2026-09-12 15:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 15:12</t>
+          <t>更新时间: 2026-09-12 16:18</t>
         </is>
       </c>
     </row>
